--- a/Thermodynamic calculations/Reaction/reaction.xlsx
+++ b/Thermodynamic calculations/Reaction/reaction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIT Dropbox\Wande Cairang\XJTU research\Mo-Nb\Draft\XRD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88C84491-1CC1-4A66-9882-677448F09F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F9CB3-E630-49AE-82DD-D825B02B34A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3450" windowWidth="29040" windowHeight="15720" xr2:uid="{0A61118D-6C91-4A79-B918-AA582F75CA1A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0A61118D-6C91-4A79-B918-AA582F75CA1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="8">
   <si>
     <t>MoO2</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>Nb2O5</t>
+  </si>
+  <si>
+    <t>per mole O2</t>
+  </si>
+  <si>
+    <t>Per mole O2</t>
   </si>
 </sst>
 </file>
@@ -426,16 +432,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95C2705-0E02-4DD3-9BD3-B4805722494C}">
-  <dimension ref="B1:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:Y17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" customWidth="1"/>
+    <col min="22" max="22" width="10.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -445,44 +451,59 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
       </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
       <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>3</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" t="s">
         <v>1</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" t="s">
         <v>1</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>5</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>25</v>
       </c>
@@ -493,48 +514,68 @@
         <f>C2/1000</f>
         <v>-532.04319999999996</v>
       </c>
-      <c r="F2">
+      <c r="E2">
+        <f>D2</f>
+        <v>-532.04319999999996</v>
+      </c>
+      <c r="G2">
         <v>25</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>-1336255.3</v>
       </c>
-      <c r="H2">
-        <f>G2/1000</f>
+      <c r="I2">
+        <f>H2/1000</f>
         <v>-1336.2553</v>
       </c>
       <c r="J2">
+        <f>I2/3</f>
+        <v>-445.41843333333333</v>
+      </c>
+      <c r="L2">
         <v>25</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>-783878.7</v>
       </c>
-      <c r="L2">
-        <f>K2/1000</f>
+      <c r="N2">
+        <f>M2/1000</f>
         <v>-783.87869999999998</v>
       </c>
-      <c r="N2">
+      <c r="O2">
+        <f>N2</f>
+        <v>-783.87869999999998</v>
+      </c>
+      <c r="Q2">
         <v>25</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>-739207.3</v>
       </c>
-      <c r="P2">
-        <f>O2/1000</f>
+      <c r="S2">
+        <f>R2/1000</f>
         <v>-739.20730000000003</v>
       </c>
-      <c r="R2">
+      <c r="T2">
+        <f>S2</f>
+        <v>-739.20730000000003</v>
+      </c>
+      <c r="V2">
         <v>25</v>
       </c>
-      <c r="S2">
+      <c r="W2">
         <v>-3531796.1</v>
       </c>
-      <c r="T2">
-        <f>S2/1000</f>
+      <c r="X2">
+        <f>W2/1000</f>
         <v>-3531.7961</v>
       </c>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y2">
+        <f>X2/5</f>
+        <v>-706.35922000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>125</v>
       </c>
@@ -545,48 +586,68 @@
         <f t="shared" ref="D3:D12" si="0">C3/1000</f>
         <v>-513.39819999999997</v>
       </c>
-      <c r="F3">
+      <c r="E3">
+        <f t="shared" ref="E3:E12" si="1">D3</f>
+        <v>-513.39819999999997</v>
+      </c>
+      <c r="G3">
         <v>125</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>-1284858.5</v>
       </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H13" si="1">G3/1000</f>
+      <c r="I3">
+        <f t="shared" ref="I3:I13" si="2">H3/1000</f>
         <v>-1284.8585</v>
       </c>
       <c r="J3">
+        <f t="shared" ref="J3:J13" si="3">I3/3</f>
+        <v>-428.2861666666667</v>
+      </c>
+      <c r="L3">
         <v>125</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>-765362.3</v>
       </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L12" si="2">K3/1000</f>
+      <c r="N3">
+        <f t="shared" ref="N3:N12" si="4">M3/1000</f>
         <v>-765.3623</v>
       </c>
-      <c r="N3">
+      <c r="O3">
+        <f t="shared" ref="O3:O12" si="5">N3</f>
+        <v>-765.3623</v>
+      </c>
+      <c r="Q3">
         <v>125</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <v>-720585.8</v>
       </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P13" si="3">O3/1000</f>
+      <c r="S3">
+        <f t="shared" ref="S3:S13" si="6">R3/1000</f>
         <v>-720.58580000000006</v>
       </c>
-      <c r="R3">
+      <c r="T3">
+        <f t="shared" ref="T3:T13" si="7">S3</f>
+        <v>-720.58580000000006</v>
+      </c>
+      <c r="V3">
         <v>125</v>
       </c>
-      <c r="S3">
+      <c r="W3">
         <v>-3442540.8</v>
       </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T12" si="4">S3/1000</f>
+      <c r="X3">
+        <f t="shared" ref="X3:X12" si="8">W3/1000</f>
         <v>-3442.5407999999998</v>
       </c>
-    </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y12" si="9">X3/5</f>
+        <v>-688.50815999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>225</v>
       </c>
@@ -597,48 +658,68 @@
         <f t="shared" si="0"/>
         <v>-494.95359999999999</v>
       </c>
-      <c r="F4">
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>-494.95359999999999</v>
+      </c>
+      <c r="G4">
         <v>225</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>-1234090.1000000001</v>
       </c>
-      <c r="H4">
-        <f t="shared" si="1"/>
+      <c r="I4">
+        <f t="shared" si="2"/>
         <v>-1234.0901000000001</v>
       </c>
       <c r="J4">
+        <f t="shared" si="3"/>
+        <v>-411.36336666666671</v>
+      </c>
+      <c r="L4">
         <v>225</v>
       </c>
-      <c r="K4" s="1">
+      <c r="M4" s="1">
         <v>-747022.5</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="2"/>
+      <c r="N4">
+        <f t="shared" si="4"/>
         <v>-747.02250000000004</v>
       </c>
-      <c r="N4">
+      <c r="O4">
+        <f t="shared" si="5"/>
+        <v>-747.02250000000004</v>
+      </c>
+      <c r="Q4">
         <v>225</v>
       </c>
-      <c r="O4" s="1">
+      <c r="R4" s="1">
         <v>-702159.9</v>
       </c>
-      <c r="P4">
-        <f t="shared" si="3"/>
+      <c r="S4">
+        <f t="shared" si="6"/>
         <v>-702.15989999999999</v>
       </c>
-      <c r="R4">
+      <c r="T4">
+        <f t="shared" si="7"/>
+        <v>-702.15989999999999</v>
+      </c>
+      <c r="V4">
         <v>225</v>
       </c>
-      <c r="S4" s="1">
+      <c r="W4" s="1">
         <v>-3354212.5</v>
       </c>
-      <c r="T4">
-        <f t="shared" si="4"/>
+      <c r="X4">
+        <f t="shared" si="8"/>
         <v>-3354.2125000000001</v>
       </c>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y4">
+        <f t="shared" si="9"/>
+        <v>-670.84249999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>325</v>
       </c>
@@ -649,48 +730,68 @@
         <f t="shared" si="0"/>
         <v>-476.72709999999995</v>
       </c>
-      <c r="F5">
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>-476.72709999999995</v>
+      </c>
+      <c r="G5">
         <v>325</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-1183932.1000000001</v>
       </c>
-      <c r="H5">
-        <f t="shared" si="1"/>
+      <c r="I5">
+        <f t="shared" si="2"/>
         <v>-1183.9321</v>
       </c>
       <c r="J5">
+        <f t="shared" si="3"/>
+        <v>-394.64403333333331</v>
+      </c>
+      <c r="L5">
         <v>325</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>-728856.4</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="2"/>
+      <c r="N5">
+        <f t="shared" si="4"/>
         <v>-728.85640000000001</v>
       </c>
-      <c r="N5">
+      <c r="O5">
+        <f t="shared" si="5"/>
+        <v>-728.85640000000001</v>
+      </c>
+      <c r="Q5">
         <v>325</v>
       </c>
-      <c r="O5" s="1">
+      <c r="R5" s="1">
         <v>-683948.3</v>
       </c>
-      <c r="P5">
-        <f t="shared" si="3"/>
+      <c r="S5">
+        <f t="shared" si="6"/>
         <v>-683.94830000000002</v>
       </c>
-      <c r="R5">
+      <c r="T5">
+        <f t="shared" si="7"/>
+        <v>-683.94830000000002</v>
+      </c>
+      <c r="V5">
         <v>325</v>
       </c>
-      <c r="S5" s="1">
+      <c r="W5" s="1">
         <v>-3266850.3</v>
       </c>
-      <c r="T5">
-        <f t="shared" si="4"/>
+      <c r="X5">
+        <f t="shared" si="8"/>
         <v>-3266.8502999999996</v>
       </c>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y5">
+        <f t="shared" si="9"/>
+        <v>-653.37005999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>425</v>
       </c>
@@ -701,48 +802,68 @@
         <f t="shared" si="0"/>
         <v>-458.71129999999999</v>
       </c>
-      <c r="F6">
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>-458.71129999999999</v>
+      </c>
+      <c r="G6">
         <v>425</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>-1134349.3999999999</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
+      <c r="I6">
+        <f t="shared" si="2"/>
         <v>-1134.3493999999998</v>
       </c>
       <c r="J6">
+        <f t="shared" si="3"/>
+        <v>-378.11646666666661</v>
+      </c>
+      <c r="L6">
         <v>425</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>-710849.2</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
+      <c r="N6">
+        <f t="shared" si="4"/>
         <v>-710.8492</v>
       </c>
-      <c r="N6">
+      <c r="O6">
+        <f t="shared" si="5"/>
+        <v>-710.8492</v>
+      </c>
+      <c r="Q6">
         <v>425</v>
       </c>
-      <c r="O6" s="1">
+      <c r="R6" s="1">
         <v>-665956.5</v>
       </c>
-      <c r="P6">
-        <f t="shared" si="3"/>
+      <c r="S6">
+        <f t="shared" si="6"/>
         <v>-665.95650000000001</v>
       </c>
-      <c r="R6">
+      <c r="T6">
+        <f t="shared" si="7"/>
+        <v>-665.95650000000001</v>
+      </c>
+      <c r="V6">
         <v>425</v>
       </c>
-      <c r="S6" s="1">
+      <c r="W6" s="1">
         <v>-3180410.4</v>
       </c>
-      <c r="T6">
-        <f t="shared" si="4"/>
+      <c r="X6">
+        <f t="shared" si="8"/>
         <v>-3180.4103999999998</v>
       </c>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y6">
+        <f t="shared" si="9"/>
+        <v>-636.08207999999991</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>525</v>
       </c>
@@ -753,48 +874,68 @@
         <f t="shared" si="0"/>
         <v>-440.89590000000004</v>
       </c>
-      <c r="F7">
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>-440.89590000000004</v>
+      </c>
+      <c r="G7">
         <v>525</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>-1085322.6000000001</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
+      <c r="I7">
+        <f t="shared" si="2"/>
         <v>-1085.3226000000002</v>
       </c>
       <c r="J7">
+        <f t="shared" si="3"/>
+        <v>-361.77420000000006</v>
+      </c>
+      <c r="L7">
         <v>525</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>-692987.1</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
+      <c r="N7">
+        <f t="shared" si="4"/>
         <v>-692.98709999999994</v>
       </c>
-      <c r="N7">
+      <c r="O7">
+        <f t="shared" si="5"/>
+        <v>-692.98709999999994</v>
+      </c>
+      <c r="Q7">
         <v>525</v>
       </c>
-      <c r="O7" s="1">
+      <c r="R7" s="1">
         <v>-648189.80000000005</v>
       </c>
-      <c r="P7">
-        <f t="shared" si="3"/>
+      <c r="S7">
+        <f t="shared" si="6"/>
         <v>-648.18979999999999</v>
       </c>
-      <c r="R7">
+      <c r="T7">
+        <f t="shared" si="7"/>
+        <v>-648.18979999999999</v>
+      </c>
+      <c r="V7">
         <v>525</v>
       </c>
-      <c r="S7" s="1">
+      <c r="W7" s="1">
         <v>-3094826.7</v>
       </c>
-      <c r="T7">
-        <f t="shared" si="4"/>
+      <c r="X7">
+        <f t="shared" si="8"/>
         <v>-3094.8267000000001</v>
       </c>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y7">
+        <f t="shared" si="9"/>
+        <v>-618.96533999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>625</v>
       </c>
@@ -805,49 +946,69 @@
         <f t="shared" si="0"/>
         <v>-423.27249999999998</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8">
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>-423.27249999999998</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8">
         <v>625</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>-1036846.7</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
+      <c r="I8">
+        <f t="shared" si="2"/>
         <v>-1036.8467000000001</v>
       </c>
       <c r="J8">
+        <f t="shared" si="3"/>
+        <v>-345.61556666666667</v>
+      </c>
+      <c r="L8">
         <v>625</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>-675260</v>
       </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
+      <c r="N8">
+        <f t="shared" si="4"/>
         <v>-675.26</v>
       </c>
-      <c r="N8">
+      <c r="O8">
+        <f t="shared" si="5"/>
+        <v>-675.26</v>
+      </c>
+      <c r="Q8">
         <v>625</v>
       </c>
-      <c r="O8" s="1">
+      <c r="R8" s="1">
         <v>-630654.6</v>
       </c>
-      <c r="P8">
-        <f t="shared" si="3"/>
+      <c r="S8">
+        <f t="shared" si="6"/>
         <v>-630.65459999999996</v>
       </c>
-      <c r="R8">
+      <c r="T8">
+        <f t="shared" si="7"/>
+        <v>-630.65459999999996</v>
+      </c>
+      <c r="V8">
         <v>625</v>
       </c>
-      <c r="S8" s="1">
+      <c r="W8" s="1">
         <v>-3010026.6</v>
       </c>
-      <c r="T8">
-        <f t="shared" si="4"/>
+      <c r="X8">
+        <f t="shared" si="8"/>
         <v>-3010.0266000000001</v>
       </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y8">
+        <f t="shared" si="9"/>
+        <v>-602.00531999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>725</v>
       </c>
@@ -858,49 +1019,69 @@
         <f t="shared" si="0"/>
         <v>-405.83509999999995</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9">
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>-405.83509999999995</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9">
         <v>725</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>-988926.8</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
+      <c r="I9">
+        <f t="shared" si="2"/>
         <v>-988.92680000000007</v>
       </c>
       <c r="J9">
+        <f t="shared" si="3"/>
+        <v>-329.64226666666667</v>
+      </c>
+      <c r="L9">
         <v>725</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>-657660.1</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
+      <c r="N9">
+        <f t="shared" si="4"/>
         <v>-657.66009999999994</v>
       </c>
-      <c r="N9">
+      <c r="O9">
+        <f t="shared" si="5"/>
+        <v>-657.66009999999994</v>
+      </c>
+      <c r="Q9">
         <v>725</v>
       </c>
-      <c r="O9" s="1">
+      <c r="R9" s="1">
         <v>-613358</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="3"/>
+      <c r="S9">
+        <f t="shared" si="6"/>
         <v>-613.35799999999995</v>
       </c>
-      <c r="R9">
+      <c r="T9">
+        <f t="shared" si="7"/>
+        <v>-613.35799999999995</v>
+      </c>
+      <c r="V9">
         <v>725</v>
       </c>
-      <c r="S9" s="1">
+      <c r="W9" s="1">
         <v>-2925940.9</v>
       </c>
-      <c r="T9">
-        <f t="shared" si="4"/>
+      <c r="X9">
+        <f t="shared" si="8"/>
         <v>-2925.9409000000001</v>
       </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y9">
+        <f t="shared" si="9"/>
+        <v>-585.18817999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>825</v>
       </c>
@@ -911,49 +1092,69 @@
         <f t="shared" si="0"/>
         <v>-388.57959999999997</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10">
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>-388.57959999999997</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10">
         <v>800.85</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>-952956.9</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
+      <c r="I10">
+        <f t="shared" si="2"/>
         <v>-952.95690000000002</v>
       </c>
       <c r="J10">
+        <f t="shared" si="3"/>
+        <v>-317.65230000000003</v>
+      </c>
+      <c r="L10">
         <v>825</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>-640182</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
+      <c r="N10">
+        <f t="shared" si="4"/>
         <v>-640.18200000000002</v>
       </c>
-      <c r="N10">
+      <c r="O10">
+        <f t="shared" si="5"/>
+        <v>-640.18200000000002</v>
+      </c>
+      <c r="Q10">
         <v>814.66</v>
       </c>
-      <c r="O10" s="1">
+      <c r="R10" s="1">
         <v>-598059.4</v>
       </c>
-      <c r="P10">
-        <f t="shared" si="3"/>
+      <c r="S10">
+        <f t="shared" si="6"/>
         <v>-598.05939999999998</v>
       </c>
-      <c r="R10">
+      <c r="T10">
+        <f t="shared" si="7"/>
+        <v>-598.05939999999998</v>
+      </c>
+      <c r="V10">
         <v>825</v>
       </c>
-      <c r="S10" s="1">
+      <c r="W10" s="1">
         <v>-2842505.5</v>
       </c>
-      <c r="T10">
-        <f t="shared" si="4"/>
+      <c r="X10">
+        <f t="shared" si="8"/>
         <v>-2842.5055000000002</v>
       </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y10">
+        <f t="shared" si="9"/>
+        <v>-568.50110000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>925</v>
       </c>
@@ -964,49 +1165,69 @@
         <f t="shared" si="0"/>
         <v>-371.50329999999997</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11">
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>-371.50329999999997</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11">
         <v>825</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>-943763.9</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
+      <c r="I11">
+        <f t="shared" si="2"/>
         <v>-943.76390000000004</v>
       </c>
       <c r="J11">
+        <f t="shared" si="3"/>
+        <v>-314.58796666666666</v>
+      </c>
+      <c r="L11">
         <v>925</v>
       </c>
-      <c r="K11" s="1">
+      <c r="M11" s="1">
         <v>-622821.1</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
+      <c r="N11">
+        <f t="shared" si="4"/>
         <v>-622.8211</v>
       </c>
-      <c r="N11">
+      <c r="O11">
+        <f t="shared" si="5"/>
+        <v>-622.8211</v>
+      </c>
+      <c r="Q11">
         <v>825</v>
       </c>
-      <c r="O11" s="1">
+      <c r="R11" s="1">
         <v>-596340</v>
       </c>
-      <c r="P11">
-        <f t="shared" si="3"/>
+      <c r="S11">
+        <f t="shared" si="6"/>
         <v>-596.34</v>
       </c>
-      <c r="R11">
+      <c r="T11">
+        <f t="shared" si="7"/>
+        <v>-596.34</v>
+      </c>
+      <c r="V11">
         <v>925</v>
       </c>
-      <c r="S11" s="1">
+      <c r="W11" s="1">
         <v>-2759660.7</v>
       </c>
-      <c r="T11">
-        <f t="shared" si="4"/>
+      <c r="X11">
+        <f t="shared" si="8"/>
         <v>-2759.6607000000004</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="Y11">
+        <f t="shared" si="9"/>
+        <v>-551.93214000000012</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>1000</v>
       </c>
@@ -1017,82 +1238,110 @@
         <f t="shared" si="0"/>
         <v>-358.81290000000001</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12">
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>-358.81290000000001</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12">
         <v>925</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>-906193</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="1"/>
+      <c r="I12">
+        <f t="shared" si="2"/>
         <v>-906.19299999999998</v>
       </c>
       <c r="J12">
+        <f t="shared" si="3"/>
+        <v>-302.06433333333331</v>
+      </c>
+      <c r="L12">
         <v>1000</v>
       </c>
-      <c r="K12" s="1">
+      <c r="M12" s="1">
         <v>-609875</v>
       </c>
-      <c r="L12">
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>-609.875</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="5"/>
+        <v>-609.875</v>
+      </c>
+      <c r="Q12">
+        <v>925</v>
+      </c>
+      <c r="R12">
+        <v>-579852.80000000005</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="6"/>
+        <v>-579.8528</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="7"/>
+        <v>-579.8528</v>
+      </c>
+      <c r="V12">
+        <v>1000</v>
+      </c>
+      <c r="W12" s="1">
+        <v>-2697882.3</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="8"/>
+        <v>-2697.8822999999998</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="9"/>
+        <v>-539.57646</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="F13" s="1"/>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="1">
+        <v>-878501.1</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="2"/>
-        <v>-609.875</v>
-      </c>
-      <c r="N12">
-        <v>925</v>
-      </c>
-      <c r="O12">
-        <v>-579852.80000000005</v>
-      </c>
-      <c r="P12">
+        <v>-878.50109999999995</v>
+      </c>
+      <c r="J13">
         <f t="shared" si="3"/>
-        <v>-579.8528</v>
-      </c>
-      <c r="R12">
+        <v>-292.83369999999996</v>
+      </c>
+      <c r="Q13">
         <v>1000</v>
       </c>
-      <c r="S12" s="1">
-        <v>-2697882.3</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="4"/>
-        <v>-2697.8822999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="E13" s="1"/>
-      <c r="F13">
-        <v>1000</v>
-      </c>
-      <c r="G13" s="1">
-        <v>-878501.1</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="1"/>
-        <v>-878.50109999999995</v>
-      </c>
-      <c r="N13">
-        <v>1000</v>
-      </c>
-      <c r="O13">
+      <c r="R13">
         <v>-567628.30000000005</v>
       </c>
-      <c r="P13">
-        <f t="shared" si="3"/>
+      <c r="S13">
+        <f t="shared" si="6"/>
         <v>-567.62830000000008</v>
       </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="1"/>
+      <c r="T13">
+        <f t="shared" si="7"/>
+        <v>-567.62830000000008</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
